--- a/output/2026-10-04_Malesia_Sabah_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-10-04_Malesia_Sabah_Utensilerie_e_Macchine_Utensili.xlsx
@@ -494,8 +494,6 @@
           <t>Utensilerie e Macchine Utensili</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>Distributore/rivenditore B2B di utensili e hardware (power tools Milwaukee), vendita all'ingrosso con termini di credito 30-60gg. Indirizzo confermato: Lot 15, Ground Floor, Lorong Mutiara Inanam, Komplek Mutiara, 88450 Kota Kinabalu. Sito web proprio non reperito; riferimento = profilo su marketplace B2B Lapasar. Telefono/email non reperibili da fonte pubblica.</t>
@@ -503,7 +501,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>

--- a/output/2026-10-04_Malesia_Sabah_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-10-04_Malesia_Sabah_Utensilerie_e_Macchine_Utensili.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Distributore/rivenditore B2B di utensili e hardware (power tools Milwaukee), vendita all'ingrosso con termini di credito 30-60gg. Indirizzo confermato: Lot 15, Ground Floor, Lorong Mutiara Inanam, Komplek Mutiara, 88450 Kota Kinabalu. Sito web proprio non reperito; riferimento = profilo su marketplace B2B Lapasar. Telefono/email non reperibili da fonte pubblica.</t>
+          <t>Distributore/rivenditore B2B di utensili e hardware (power tools Milwaukee), vendita all'ingrosso con termini di credito 30-60gg. Indirizzo confermato: Lot 15, Ground Floor, Lorong Mutiara Inanam, Komplek Mutiara, 88450 Kota Kinabalu. Sito web proprio non reperito; riferimento = profilo su marketplace B2B Lapasar. Telefono/email non reperibili da fonte pubblica. [DUPLICATO — vedi anche: 2026-10-04_10_Malesia_Sabah_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
